--- a/www/download/IND.surplus_value.empe_ls.r.pc.rpA1.xlsx
+++ b/www/download/IND.surplus_value.empe_ls.r.pc.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>107.38</t>
+          <t>1.07378448954364</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>102.07</t>
+          <t>1.0207178751892</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>109.96</t>
+          <t>1.09956832305726</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>110.13</t>
+          <t>1.10127506902342</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>99.85</t>
+          <t>0.998508992990429</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>109.52</t>
+          <t>1.09518560681988</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>116.8</t>
+          <t>1.16797586628252</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>107.18</t>
+          <t>1.07176740452049</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>0.948556641071273</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>70.69</t>
+          <t>0.706943193615143</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>0.630028417412454</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>66.63</t>
+          <t>0.66627400590362</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>63.13</t>
+          <t>0.631349402732072</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>0.801251907808676</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>0.877676783013265</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>0.541469958319253</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>61.09</t>
+          <t>0.610895018760925</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>0.896188293144859</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>0.888886994045125</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>87.09</t>
+          <t>0.870938756270058</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>95.71</t>
+          <t>0.957088451286063</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>94.89</t>
+          <t>0.948882364406661</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>0.930171857449166</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>0.383038268992308</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>0.699204078724377</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>0.683932901876373</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>0.683663546631818</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>79.83</t>
+          <t>0.798325556651114</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>0.965006653810389</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>1.11898439481786</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-0.0939221982882918</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-0.109034042393486</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-0.0635704481636112</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-0.0548441155379916</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-0.141623952963052</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>-0.144956007381839</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-19.02</t>
+          <t>-0.190159197297107</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-0.256858004193747</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-46.35</t>
+          <t>-0.463537340175325</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-41.09</t>
+          <t>-0.410860295818376</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-39.59</t>
+          <t>-0.395906316943549</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-38.34</t>
+          <t>-0.383350327937552</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-0.323654286733521</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>-0.247895898681259</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-28.69</t>
+          <t>-0.286918690563232</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>302.26</t>
+          <t>3.02261757202779</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>346.73</t>
+          <t>3.46726327293839</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>401.44</t>
+          <t>4.01436145793894</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>315.02</t>
+          <t>3.15015351974267</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>368.01</t>
+          <t>3.68009133267386</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>398.3</t>
+          <t>3.98304083558451</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>391.99</t>
+          <t>3.91988662234049</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>419.86</t>
+          <t>4.19859317701528</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>351.48</t>
+          <t>3.51484157567804</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>4.55995053231917</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>477.95</t>
+          <t>4.77953512293162</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>502.67</t>
+          <t>5.02673916925714</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>475.66</t>
+          <t>4.75657582204654</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>464.37</t>
+          <t>4.64365553329541</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>409.56</t>
+          <t>4.09558917327957</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>578.68</t>
+          <t>5.78684212348705</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>593.94</t>
+          <t>5.93939636116512</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>633.03</t>
+          <t>6.33029982565266</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>636.42</t>
+          <t>6.36424462544731</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>726.09</t>
+          <t>7.26094607484856</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>718.89</t>
+          <t>7.18889036647889</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>757.87</t>
+          <t>7.5786765076821</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>803.34</t>
+          <t>8.03337246660126</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>807.45</t>
+          <t>8.0745341647478</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>784.84</t>
+          <t>7.84837157714647</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>735.23</t>
+          <t>7.35230693531379</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>734.4</t>
+          <t>7.34401702081007</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>733.31</t>
+          <t>7.33310698744897</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>704.5</t>
+          <t>7.0449805243683</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>694.24</t>
+          <t>6.94244193546423</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>143.87</t>
+          <t>1.43865697778774</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>159.92</t>
+          <t>1.59918297012436</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>172.11</t>
+          <t>1.72112368445034</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>158.75</t>
+          <t>1.5875496297636</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>151.45</t>
+          <t>1.51445537246035</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>134.96</t>
+          <t>1.34956904960172</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>122.44</t>
+          <t>1.22436072732374</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>127.47</t>
+          <t>1.27474154813343</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>117.14</t>
+          <t>1.17138108032157</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>111.28</t>
+          <t>1.1128424250995</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>0.974998431941095</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>90.84</t>
+          <t>0.908405635721302</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>100.22</t>
+          <t>1.00221221138618</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>106.72</t>
+          <t>1.06724766957038</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>120.9</t>
+          <t>1.20896683580671</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-25.09</t>
+          <t>-0.250938639676746</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-21.8</t>
+          <t>-0.217960775804237</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-0.171940633144986</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-0.110182621741302</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.0262686589778068</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>0.0812668219673098</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>0.194923323833657</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>0.304386276202005</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.397559972061938</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>0.42153171154116</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>51.23</t>
+          <t>0.512299413326848</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>59.44</t>
+          <t>0.594382475707616</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>0.737538894262651</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>0.765051912498751</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>0.823113016922829</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>172.32</t>
+          <t>1.72320940742359</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>164.57</t>
+          <t>1.6456866247918</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>203.72</t>
+          <t>2.03715491660337</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>1.90871235257712</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>166.45</t>
+          <t>1.66452173022537</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>180.22</t>
+          <t>1.80216802711143</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>158.53</t>
+          <t>1.58530916414546</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>154.35</t>
+          <t>1.54345603789859</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>104.72</t>
+          <t>1.04723897027161</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>145.44</t>
+          <t>1.45436638039673</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>153.83</t>
+          <t>1.53826918824086</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>159.77</t>
+          <t>1.59769842148194</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>1.93498115303451</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>147.82</t>
+          <t>1.47816313997789</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>207.01</t>
+          <t>2.07009863597625</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>580.73</t>
+          <t>5.80734778625605</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>377.05</t>
+          <t>3.77046551344999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>414.81</t>
+          <t>4.14809699945219</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>404.21</t>
+          <t>4.04214213927207</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>408.76</t>
+          <t>4.08757304735063</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>420.86</t>
+          <t>4.20859612374845</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>387.53</t>
+          <t>3.87533471999453</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>355.81</t>
+          <t>3.55812203317543</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>189.65</t>
+          <t>1.89653111887434</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>291.66</t>
+          <t>2.91664478350784</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>279.77</t>
+          <t>2.79770556863003</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>295.79</t>
+          <t>2.95791824462675</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>268.34</t>
+          <t>2.68341572032316</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>266.6</t>
+          <t>2.66600927073626</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>331.15</t>
+          <t>3.3114860701748</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>0.417965226597168</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>59.33</t>
+          <t>0.593325829038362</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>0.833388971790794</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>0.77797380896779</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>70.98</t>
+          <t>0.709849295891564</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0.649957099647434</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>0.678411909325506</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.11</t>
+          <t>0.671145806847137</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>0.444971816202952</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>0.534760021431712</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>0.534533124863256</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>0.547535698220449</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>0.50568849218928</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>64.81</t>
+          <t>0.64806156244467</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>0.777820135179648</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.095822134647978</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>0.123493653188464</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>0.45901244749003</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>0.356186293350089</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>0.359134679419012</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>0.448754221050932</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.404232976835468</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>0.348878231534744</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>0.216322348776764</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>0.227767007763171</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>0.205241816909328</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>0.239775028408517</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>0.150296739907348</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>0.238812635386739</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>0.37527322658988</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>98.52</t>
+          <t>0.985199678632825</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>109.78</t>
+          <t>1.0977783008069</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>149.07</t>
+          <t>1.49072917158986</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>130.6</t>
+          <t>1.30598210897733</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>119.36</t>
+          <t>1.19357115374667</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>1.1950032851025</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>109.46</t>
+          <t>1.09456448710855</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>101.22</t>
+          <t>1.01224005408423</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>0.63233669778757</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>76.32</t>
+          <t>0.763170559669512</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>0.746689680298965</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>70.31</t>
+          <t>0.703090439201791</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>70.31</t>
+          <t>0.703096007126979</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>0.754439782567542</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>97.24</t>
+          <t>0.97239584259432</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>546.28</t>
+          <t>5.46275648678665</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>493.86</t>
+          <t>4.93859253820758</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>468.61</t>
+          <t>4.6861370258685</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>428.57</t>
+          <t>4.2856803952696</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>468.15</t>
+          <t>4.68149145697511</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>392.11</t>
+          <t>3.92113427512645</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>373.24</t>
+          <t>3.73239677521156</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>2.73402046855461</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>1.36302271437054</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>204.51</t>
+          <t>2.04512436373032</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>223.21</t>
+          <t>2.23207754735065</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>216.65</t>
+          <t>2.16646768023983</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>168.03</t>
+          <t>1.68030732060913</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>128.37</t>
+          <t>1.28368895536418</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>140.22</t>
+          <t>1.40218889273709</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.429778858029916</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>0.409065351884138</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>0.687372405005517</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>63.99</t>
+          <t>0.639885364969683</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>66.39</t>
+          <t>0.663872317796626</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>86.28</t>
+          <t>0.862804993598142</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>0.79821203836436</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.07</t>
+          <t>0.790710239035032</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>0.494975724674651</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>0.556543399544837</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.528398323749983</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>47.91</t>
+          <t>0.47910377745003</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>0.468573276092316</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>0.477175760666443</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>57.17</t>
+          <t>0.571714374076839</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>0.579737710108716</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>61.73</t>
+          <t>0.617275723858498</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>0.847968512156044</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>66.83</t>
+          <t>0.668306702024756</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>0.559774757558174</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>0.553880878409201</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>0.476742053474395</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>0.38677600667025</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>0.0591592823520695</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>0.235853729922965</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>0.223028663815707</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>24.17</t>
+          <t>0.241666338204119</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>0.295885038480443</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.345496424800305</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>0.459456253253686</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>0.945908301627282</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>0.939821147824931</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>113.27</t>
+          <t>1.13271641235788</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>1.0111915703661</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>89.66</t>
+          <t>0.896613237340779</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>83.01</t>
+          <t>0.830082497697944</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>0.736555453960848</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>0.672826266969447</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>0.57105212755821</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>48.54</t>
+          <t>0.485397319314028</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>0.485035357275391</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>0.485081778309014</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>0.521115638501096</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>0.716824883921534</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>0.850104432335062</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>189.6</t>
+          <t>1.89604151774819</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>183.43</t>
+          <t>1.83428920568902</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>203.63</t>
+          <t>2.03634941073617</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>215.35</t>
+          <t>2.1534630734664</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>206.48</t>
+          <t>2.06477708326113</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>200.35</t>
+          <t>2.0035315099789</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>219.44</t>
+          <t>2.19440228066931</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>179.13</t>
+          <t>1.79132031333849</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>142.31</t>
+          <t>1.42310617820242</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>174.38</t>
+          <t>1.7437777677008</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>180.51</t>
+          <t>1.80510788146435</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>1.68499620109118</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>159.01</t>
+          <t>1.59010208883195</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>152.53</t>
+          <t>1.52533419860636</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>149.85</t>
+          <t>1.4984640283597</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>284.73</t>
+          <t>2.84729256567773</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>306.97</t>
+          <t>3.06972569628785</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>336.48</t>
+          <t>3.36475746227467</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>350.83</t>
+          <t>3.50829554858066</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>360.39</t>
+          <t>3.60390319358488</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>346.08</t>
+          <t>3.46077805083501</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>361.06</t>
+          <t>3.61061170167986</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>328.64</t>
+          <t>3.28642645088764</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>158.15</t>
+          <t>1.58153321551007</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>381.27</t>
+          <t>3.8127368149581</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>390.29</t>
+          <t>3.90287905169245</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>423.44</t>
+          <t>4.23438235780916</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>400.21</t>
+          <t>4.00210676372185</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>474.36</t>
+          <t>4.74356696301837</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>525.46</t>
+          <t>5.25461915535083</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>149.08</t>
+          <t>1.49081311942167</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>144.12</t>
+          <t>1.44120955553774</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>187.74</t>
+          <t>1.87743887670766</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>183.88</t>
+          <t>1.83882266572251</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>178.55</t>
+          <t>1.78545238008871</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>173.27</t>
+          <t>1.73267091311734</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>182.68</t>
+          <t>1.82680210067027</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>187.58</t>
+          <t>1.87581712332645</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>1.62195341816081</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>183.02</t>
+          <t>1.83017133819139</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>1.70593185002197</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>154.43</t>
+          <t>1.54434649810691</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>145.6</t>
+          <t>1.45599571605418</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>149.98</t>
+          <t>1.4998300438273</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>1.38688041932926</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>1.38504194472325</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1.63004910325563</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>155.8</t>
+          <t>1.55801902479732</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>170.73</t>
+          <t>1.70731881138271</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>182.24</t>
+          <t>1.8224040706871</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>197.16</t>
+          <t>1.97162640647698</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>195.49</t>
+          <t>1.95490413421538</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>202.14</t>
+          <t>2.0214412643458</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>190.06</t>
+          <t>1.90059804279926</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>176.24</t>
+          <t>1.76244966097219</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>163.45</t>
+          <t>1.63451374931141</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>156.41</t>
+          <t>1.56409940765607</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>157.41</t>
+          <t>1.57408565229072</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>166.94</t>
+          <t>1.66944022213502</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>155.71</t>
+          <t>1.55713682080775</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>85.51</t>
+          <t>0.855145704356386</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>0.875024017140906</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>120.9</t>
+          <t>1.20899275208998</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>136.09</t>
+          <t>1.36091111392902</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>141.15</t>
+          <t>1.41154220288263</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>142.47</t>
+          <t>1.42473769112498</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>123.11</t>
+          <t>1.23111552059993</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>112.85</t>
+          <t>1.12848369361291</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>134.73</t>
+          <t>1.34725920013768</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>149.27</t>
+          <t>1.49273929976549</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>115.68</t>
+          <t>1.15683761956333</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>142.77</t>
+          <t>1.42767212053896</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>1.03707226363668</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>94.27</t>
+          <t>0.942653939952659</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>75.98</t>
+          <t>0.759774686008324</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>0.728618249954206</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>82.67</t>
+          <t>0.826655705071517</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>103.65</t>
+          <t>1.03654928822935</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>108.31</t>
+          <t>1.08314926771459</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>1.07598061207998</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>111.7</t>
+          <t>1.11700702408258</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>102.55</t>
+          <t>1.02547630061812</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>97.68</t>
+          <t>0.97683260155584</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58.49</t>
+          <t>0.584853525188313</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>70.09</t>
+          <t>0.70085238211508</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>70.63</t>
+          <t>0.706315535680469</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>0.697836741976243</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>0.756746697222075</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>0.797793348801571</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>0.987362362718736</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.35</t>
+          <t>0.523523754129574</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>74.86</t>
+          <t>0.748605802395751</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>0.925367296670426</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>99.15</t>
+          <t>0.991513824082063</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>0.86389101690702</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>0.749361305725631</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>79.67</t>
+          <t>0.796742001058719</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>91.93</t>
+          <t>0.919270643525615</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>0.850422305329374</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>78.41</t>
+          <t>0.784089791897743</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>0.797279779056867</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>0.904652837376627</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>110.06</t>
+          <t>1.10056648989815</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>116.22</t>
+          <t>1.16220758957217</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>109.09</t>
+          <t>1.09087441426613</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>124.19</t>
+          <t>1.24186718239878</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>133.59</t>
+          <t>1.33586114366829</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>158.63</t>
+          <t>1.58632554289444</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>192.42</t>
+          <t>1.92420891460249</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>191.3</t>
+          <t>1.91302313429585</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>183.36</t>
+          <t>1.83361590650058</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>204.19</t>
+          <t>2.041875681485</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>200.23</t>
+          <t>2.00231924770335</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>182.23</t>
+          <t>1.82227555875435</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>184.46</t>
+          <t>1.84460629583478</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>174.36</t>
+          <t>1.7436247403155</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>166.62</t>
+          <t>1.66618868484313</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>172.73</t>
+          <t>1.72726514378811</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>198.12</t>
+          <t>1.9812254482075</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>217.73</t>
+          <t>2.17729878774531</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>400.55</t>
+          <t>4.0055319839796</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>363.13</t>
+          <t>3.63131394438709</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>359.59</t>
+          <t>3.59588636524316</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>309.48</t>
+          <t>3.09475539983214</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>298.34</t>
+          <t>2.98343275413329</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>299.37</t>
+          <t>2.99374063731132</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>287.75</t>
+          <t>2.87754964532357</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>282.01</t>
+          <t>2.82010333836811</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1.81995450069856</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>297.66</t>
+          <t>2.97663244738945</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>2.90002345258372</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>275.84</t>
+          <t>2.75844151655648</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>222.96</t>
+          <t>2.22959095541316</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>188.11</t>
+          <t>1.88108302380782</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>193.38</t>
+          <t>1.93382370299225</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>0.302521834852266</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>0.518675142082737</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>83.49</t>
+          <t>0.834926535632163</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>0.976147778734628</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>102.02</t>
+          <t>1.0201660311443</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>110.16</t>
+          <t>1.10162962270251</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>128.85</t>
+          <t>1.28847579266396</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>1.12091287387851</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>0.523713756555846</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>94.42</t>
+          <t>0.944247303464048</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>0.865886363999526</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>0.913603853149435</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>119.95</t>
+          <t>1.19947423622814</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>97.49</t>
+          <t>0.974939081851981</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>1.46203339252583</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>385.53</t>
+          <t>3.8553499078053</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>354.59</t>
+          <t>3.54594561758618</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>344.69</t>
+          <t>3.44685603353936</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>346.5</t>
+          <t>3.46498424637006</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>363.12</t>
+          <t>3.63123216126766</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>436.84</t>
+          <t>4.36840400700529</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>445.62</t>
+          <t>4.45618760880101</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>468.12</t>
+          <t>4.68123744535726</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>312.97</t>
+          <t>3.12974567134852</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>455.83</t>
+          <t>4.55825395526707</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>388.28</t>
+          <t>3.88284589354009</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>341.51</t>
+          <t>3.41514018008474</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>290.31</t>
+          <t>2.9030655766831</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>249.07</t>
+          <t>2.49067613530943</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>327.98</t>
+          <t>3.27979616814958</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>806.76</t>
+          <t>8.06755996828013</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>891.34</t>
+          <t>8.91335682604631</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>960.81</t>
+          <t>9.60811797817109</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>893.6</t>
+          <t>8.93603296050565</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>840.03</t>
+          <t>8.40034495837532</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>814.29</t>
+          <t>8.1428738162601</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>741.92</t>
+          <t>7.41921221315719</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>761.99</t>
+          <t>7.61985373047827</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>791.82</t>
+          <t>7.91817215764867</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>830.4</t>
+          <t>8.30403146339603</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>820.21</t>
+          <t>8.20206644631853</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>906.95</t>
+          <t>9.06945605945095</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>958.09</t>
+          <t>9.58091512216081</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1028.18</t>
+          <t>10.28176310211</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1029.68</t>
+          <t>10.2968284923963</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>186.91</t>
+          <t>1.8691266363016</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>172.76</t>
+          <t>1.72763095963174</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>233.24</t>
+          <t>2.3323719375949</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>204.68</t>
+          <t>2.04677239865021</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>175.21</t>
+          <t>1.7520881493703</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>162.46</t>
+          <t>1.62462894975715</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100.57</t>
+          <t>1.00568365037575</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>122.59</t>
+          <t>1.22588545350136</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>0.671426411827122</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>161.2</t>
+          <t>1.61201211978807</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>165.42</t>
+          <t>1.65422464667945</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>173.78</t>
+          <t>1.73783091747602</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>162.94</t>
+          <t>1.62944512660009</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>1.31858076068075</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>169.16</t>
+          <t>1.69161648069818</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-0.133242148407169</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-0.0743164369795752</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>0.370473572387631</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>0.149689539085089</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.115053386836807</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>0.17260469666629</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>0.0633757736155256</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.0227404432738925</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-16.43</t>
+          <t>-0.164279782756098</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.0242623271233033</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>0.0632772306311615</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>0.0622879215996308</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>0.0553823805984524</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.00165516715081315</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.0409850763696586</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>157.72</t>
+          <t>1.57720682753326</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>148.01</t>
+          <t>1.48012314611265</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>149.2</t>
+          <t>1.49198680878657</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>138.85</t>
+          <t>1.388543794545</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>156.54</t>
+          <t>1.56543291702086</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>181.44</t>
+          <t>1.81441593820424</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>261.12</t>
+          <t>2.61124461427208</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>281.7</t>
+          <t>2.81698230378121</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>177.41</t>
+          <t>1.77408839437451</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>337.28</t>
+          <t>3.37276254202235</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>318.47</t>
+          <t>3.1847112716321</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>334.39</t>
+          <t>3.3439295845389</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>350.99</t>
+          <t>3.50988588459899</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>308.64</t>
+          <t>3.08643882069578</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>349.59</t>
+          <t>3.49588753307696</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>153.73</t>
+          <t>1.53731096024804</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>150.53</t>
+          <t>1.50532443015677</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>187.8</t>
+          <t>1.87799497330602</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>159.32</t>
+          <t>1.59319223246365</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>166.63</t>
+          <t>1.66629844255894</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>162.57</t>
+          <t>1.62565467860722</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>153.39</t>
+          <t>1.53386064099825</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>158.12</t>
+          <t>1.58121405427619</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>117.59</t>
+          <t>1.17587248174645</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>164.66</t>
+          <t>1.64660901861505</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>171.05</t>
+          <t>1.71054102288081</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>1.95997629339596</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>192.86</t>
+          <t>1.92862115758083</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>183.34</t>
+          <t>1.83342314322432</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>241.86</t>
+          <t>2.41857287092859</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>178.43</t>
+          <t>1.78428150238677</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>184.39</t>
+          <t>1.84388514509143</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>220.8</t>
+          <t>2.20795594854193</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>148.34</t>
+          <t>1.48343252644156</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>164.91</t>
+          <t>1.64914487119524</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>124.52</t>
+          <t>1.24521159651502</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>104.91</t>
+          <t>1.04907014997512</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>174.78</t>
+          <t>1.74775693832013</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>136.55</t>
+          <t>1.36552315373893</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>235.29</t>
+          <t>2.35294677968702</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>1.91653690563241</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>214.15</t>
+          <t>2.1414886624563</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>195.14</t>
+          <t>1.95137962651322</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>174.31</t>
+          <t>1.7430773924516</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>213.82</t>
+          <t>2.13817189829188</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>276.39</t>
+          <t>2.76391830086138</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>253.8</t>
+          <t>2.53803853136948</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>294.38</t>
+          <t>2.94384803723006</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>315.16</t>
+          <t>3.1515600612338</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>326.36</t>
+          <t>3.26356602852369</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>288.12</t>
+          <t>2.881206783691</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>314.38</t>
+          <t>3.14384421731825</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>290.77</t>
+          <t>2.90769997962693</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>265.91</t>
+          <t>2.65913307365053</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>264.79</t>
+          <t>2.64793879264633</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>249.69</t>
+          <t>2.49692696553416</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>255.45</t>
+          <t>2.55446333676062</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>225.23</t>
+          <t>2.2522584393792</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>186.76</t>
+          <t>1.86762045445115</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>191.6</t>
+          <t>1.9159631507893</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>637.59</t>
+          <t>6.37593745223833</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>594.16</t>
+          <t>5.94157246325828</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>620.9</t>
+          <t>6.20903019140238</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>607.47</t>
+          <t>6.07474931218348</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>659.43</t>
+          <t>6.59433174872617</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>683.82</t>
+          <t>6.83816513740971</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>656.22</t>
+          <t>6.56218529600956</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>637.36</t>
+          <t>6.37360419495966</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>291.11</t>
+          <t>2.91113312659886</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>435.03</t>
+          <t>4.35030761166568</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>460.5</t>
+          <t>4.60502467628204</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>433.33</t>
+          <t>4.33327570973193</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>340.19</t>
+          <t>3.40193514488882</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>277.93</t>
+          <t>2.7793411108827</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>204.35</t>
+          <t>2.04345677906014</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>135.55</t>
+          <t>1.35545201565966</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>143.05</t>
+          <t>1.43049212927171</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>177.51</t>
+          <t>1.77508699056264</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>162.33</t>
+          <t>1.62328216938585</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>173.83</t>
+          <t>1.7383228320531</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>172.65</t>
+          <t>1.72654612010445</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>158.32</t>
+          <t>1.5831903000353</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>153.95</t>
+          <t>1.53952564937814</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>1.3349644128986</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>149.81</t>
+          <t>1.49813592976685</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1.599997730905</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>161.47</t>
+          <t>1.61470615093207</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>1.50479435169755</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>0.896828046400824</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>100.95</t>
+          <t>1.00946342635885</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>0.485664162052157</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>0.464966412714094</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>0.697383582152194</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>0.587312510373466</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>0.601524601148276</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>0.481269380941763</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>0.470857168585027</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.424796781381781</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.200048491772422</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>0.256741789803466</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>0.216158358328286</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>0.217089269990293</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.140359313656544</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>0.297239009139861</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>50.13</t>
+          <t>0.50127364043755</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>262.03</t>
+          <t>2.62033686901393</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>232.87</t>
+          <t>2.32870679191649</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>221.8</t>
+          <t>2.21797549734462</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>215.12</t>
+          <t>2.15122916913155</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>209.77</t>
+          <t>2.09773140853125</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>256.56</t>
+          <t>2.5655634370417</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>2.96526156508801</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>344.19</t>
+          <t>3.4419348373638</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>333.13</t>
+          <t>3.33130055546109</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>300.56</t>
+          <t>3.00561132315163</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>328.31</t>
+          <t>3.28307354817799</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>354.55</t>
+          <t>3.54552238030228</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>353.8</t>
+          <t>3.53802839347667</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>170.14</t>
+          <t>1.70141658060124</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>207.69</t>
+          <t>2.07693073216063</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1.21998387562969</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>1.07337565711928</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>1.38272250507798</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>149.39</t>
+          <t>1.49386985721618</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>155.81</t>
+          <t>1.55811985990355</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>1.46700591995909</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>137.43</t>
+          <t>1.37426590717862</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>143.43</t>
+          <t>1.43425894353407</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>145.11</t>
+          <t>1.4511484978703</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>148.56</t>
+          <t>1.48559276366758</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>148.67</t>
+          <t>1.48670951606781</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>157.61</t>
+          <t>1.57607891256304</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>186.02</t>
+          <t>1.86018443404034</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>185.94</t>
+          <t>1.85939172364223</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>229.67</t>
+          <t>2.29666926281316</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>180.1</t>
+          <t>1.80096336911262</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>187.87</t>
+          <t>1.87867561220575</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>174.34</t>
+          <t>1.74341202729589</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>182.14</t>
+          <t>1.82140619523593</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>180.75</t>
+          <t>1.80750497838553</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>1.57999397387567</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>150.17</t>
+          <t>1.50167269702502</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>146.14</t>
+          <t>1.46141765259821</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>1.38267693247185</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>140.38</t>
+          <t>1.40379921629876</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>144.43</t>
+          <t>1.44433285068434</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>150.79</t>
+          <t>1.50787302748126</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>166.18</t>
+          <t>1.66181691371103</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>192.04</t>
+          <t>1.92036096264978</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>196.01</t>
+          <t>1.96005292800293</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>96.79</t>
+          <t>0.967939530294077</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>104.08</t>
+          <t>1.04075623238768</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>105.47</t>
+          <t>1.05469062226112</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>111.13</t>
+          <t>1.11128178794193</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>1.12523379137722</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>105.74</t>
+          <t>1.05739532331534</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>1.12297137683733</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>119.52</t>
+          <t>1.19517074879198</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>102.86</t>
+          <t>1.0286407641146</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>139.14</t>
+          <t>1.39137020417049</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>134.21</t>
+          <t>1.34210228446034</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>133.32</t>
+          <t>1.33320545691679</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>139.33</t>
+          <t>1.39326939383369</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>132.75</t>
+          <t>1.32748506621706</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>157.67</t>
+          <t>1.57674091207678</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>56.98</t>
+          <t>0.56983464533868</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>0.640998498905667</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0.701678687186331</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>77.19</t>
+          <t>0.771863072647358</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>0.856318733993737</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>93.04</t>
+          <t>0.930365932593491</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>100.77</t>
+          <t>1.00773917695621</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>109.06</t>
+          <t>1.09058041883288</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>1.03894390691513</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>114.55</t>
+          <t>1.14552788580469</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>116.01</t>
+          <t>1.16008518003305</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>118.74</t>
+          <t>1.18738839597627</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>126.64</t>
+          <t>1.26642175694793</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>127.12</t>
+          <t>1.27120008571975</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>135.75</t>
+          <t>1.35745093151873</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
